--- a/Configs/故事story.xlsx
+++ b/Configs/故事story.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375" firstSheet="1" activeTab="5"/>
+    <workbookView windowWidth="28800" windowHeight="12375" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="故事主表story_collection_config" sheetId="4" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="228">
   <si>
     <t>id</t>
   </si>
@@ -241,127 +241,82 @@
     <t>choices</t>
   </si>
   <si>
-    <t>options</t>
-  </si>
-  <si>
-    <t>{int id;string text;string description;int effectId;bool triggerBattle;int goldReward}[]</t>
-  </si>
-  <si>
     <t>虚空领主留下了两条道路</t>
   </si>
   <si>
     <t>101|102|103</t>
   </si>
   <si>
-    <t>101~虚空之力~吸收虚空能量，获得生命值提升~1~false~0|102~暗影之路~走入暗影，获得攻击力提升~2~false~0|103~拒绝选择~放弃力量，获得大量金币~0~false~200</t>
-  </si>
-  <si>
     <t>深渊守卫倒下了</t>
   </si>
   <si>
     <t>201|202</t>
   </si>
   <si>
-    <t>201~吸收暗能量~护盾值增加500~3~false~0|202~放弃暗能量~获得少量金币~0~false~50</t>
-  </si>
-  <si>
     <t>虚空暴君留下了力量的残渣</t>
   </si>
   <si>
     <t>301|302</t>
   </si>
   <si>
-    <t>301~净化残渣~获得攻击范围提升~4~false~0|302~吞噬残渣~获得攻击力大幅提升，但生命值降低~5~false~0</t>
-  </si>
-  <si>
     <t>暗影通道的守卫被击败</t>
   </si>
   <si>
     <t>401|402</t>
   </si>
   <si>
-    <t>401~继承暗影~获得攻击间隔缩短~6~false~0|402~摧毁暗影~获得金币奖励~0~false~100</t>
-  </si>
-  <si>
     <t>暗影的最终守护者倒下了</t>
   </si>
   <si>
     <t>501|502</t>
   </si>
   <si>
-    <t>501~探索密室~进入暗影密室~7~false~0|502~离开暗影~回到主线路径~0~false~50</t>
-  </si>
-  <si>
     <t>沉默的道路尽头出现了光芒</t>
   </si>
   <si>
     <t>601|602</t>
   </si>
   <si>
-    <t>601~追随光芒~前往营地休息~0~false~0|602~拥抱黑暗~获得暗影之力，前往商店~8~false~0</t>
-  </si>
-  <si>
     <t>旅者向你提出了请求</t>
   </si>
   <si>
     <t>701|702</t>
   </si>
   <si>
-    <t>701~帮助旅者~帮助旅者清除附近的怪物~9~true~0|702~婉言拒绝~继续赶路，获得少量补给~3~false~50</t>
-  </si>
-  <si>
     <t>裂隙深处的最终守卫倒下了</t>
   </si>
   <si>
     <t>801|802</t>
   </si>
   <si>
-    <t>801~封印裂隙~获得护盾强化~10~false~0|802~扩大裂隙~获得攻击力强化~11~false~0</t>
-  </si>
-  <si>
     <t>暗影密室中发现了神秘的宝物</t>
   </si>
   <si>
     <t>901|902</t>
   </si>
   <si>
-    <t>901~取走宝物~获得嗜血符文~12~false~0|902~摧毁宝物~获得大量金币~0~false~300</t>
-  </si>
-  <si>
     <t>第一道风暴已经平息</t>
   </si>
   <si>
     <t>1001|1002</t>
   </si>
   <si>
-    <t>1001~虚空共鸣~与虚空产生共鸣，生命值大幅提升~1~false~0|1002~暗影涌动~暗影力量涌入，攻击力提升~2~false~0</t>
-  </si>
-  <si>
     <t>第二道风暴的守卫倒下了</t>
   </si>
   <si>
     <t>1101|1102</t>
   </si>
   <si>
-    <t>1101~凝聚力量~获得技能CD减少~13~false~0|1102~分散力量~获得金币~0~false~150</t>
-  </si>
-  <si>
     <t>虚空暴君发出了最后的咆哮</t>
   </si>
   <si>
     <t>1201|1202</t>
   </si>
   <si>
-    <t>1201~终结虚空~以净化之力终结虚空的纪元~0~false~0|1202~融入虚空~接受虚空的力量，成为虚空的一部分~0~false~0</t>
-  </si>
-  <si>
     <t>歧路上的最终选择</t>
   </si>
   <si>
     <t>1301|1302</t>
-  </si>
-  <si>
-    <t>1301~回归正道~选择光明的结局~0~false~0|1302~继续歧路~走向未知的终点~0~false~0</t>
   </si>
   <si>
     <t>text</t>
@@ -2567,15 +2522,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D20"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <dimension ref="A1:C20"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
   <cols>
     <col min="2" max="2" width="27.5" customWidth="1"/>
     <col min="3" max="3" width="26.875" customWidth="1"/>
-    <col min="4" max="4" width="157" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2585,11 +2539,8 @@
       <c r="C1" t="s">
         <v>68</v>
       </c>
-      <c r="D1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+    </row>
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -2599,190 +2550,148 @@
       <c r="C2" t="s">
         <v>8</v>
       </c>
-      <c r="D2" t="s">
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C3" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:3">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C4" t="s">
-        <v>75</v>
-      </c>
-      <c r="D4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C5" t="s">
-        <v>78</v>
-      </c>
-      <c r="D5" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>81</v>
-      </c>
-      <c r="D6" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="C7" t="s">
-        <v>84</v>
-      </c>
-      <c r="D7" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="C8" t="s">
-        <v>87</v>
-      </c>
-      <c r="D8" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
       <c r="A9">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="C9" t="s">
-        <v>90</v>
-      </c>
-      <c r="D9" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
       <c r="A10">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="C10" t="s">
-        <v>93</v>
-      </c>
-      <c r="D10" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
       <c r="A11">
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="C11" t="s">
-        <v>96</v>
-      </c>
-      <c r="D11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
       <c r="A12">
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="C12" t="s">
-        <v>99</v>
-      </c>
-      <c r="D12" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
       <c r="A13">
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="C13" t="s">
-        <v>102</v>
-      </c>
-      <c r="D13" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
       <c r="A14">
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="C14" t="s">
-        <v>105</v>
-      </c>
-      <c r="D14" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
       <c r="A15">
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="C15" t="s">
-        <v>108</v>
-      </c>
-      <c r="D15" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
     </row>
     <row r="20" spans="3:3">
@@ -2814,19 +2723,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -2846,7 +2755,7 @@
         <v>6</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>115</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -2854,10 +2763,10 @@
         <v>101</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="D3" s="2">
         <v>0</v>
@@ -2874,10 +2783,10 @@
         <v>102</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="D4" s="2">
         <v>0</v>
@@ -2894,10 +2803,10 @@
         <v>103</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
       <c r="D5" s="2">
         <v>200</v>
@@ -2914,10 +2823,10 @@
         <v>201</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>123</v>
+        <v>108</v>
       </c>
       <c r="D6" s="2">
         <v>0</v>
@@ -2934,10 +2843,10 @@
         <v>202</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="D7" s="2">
         <v>50</v>
@@ -2954,10 +2863,10 @@
         <v>301</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="D8" s="2">
         <v>0</v>
@@ -2974,10 +2883,10 @@
         <v>302</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>128</v>
+        <v>113</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="D9" s="2">
         <v>0</v>
@@ -2994,10 +2903,10 @@
         <v>401</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="D10" s="2">
         <v>0</v>
@@ -3014,10 +2923,10 @@
         <v>402</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="D11" s="2">
         <v>100</v>
@@ -3034,10 +2943,10 @@
         <v>501</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="D12" s="2">
         <v>0</v>
@@ -3054,10 +2963,10 @@
         <v>502</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="D13" s="2">
         <v>50</v>
@@ -3074,10 +2983,10 @@
         <v>601</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="D14" s="2">
         <v>0</v>
@@ -3094,10 +3003,10 @@
         <v>602</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
       <c r="D15" s="2">
         <v>0</v>
@@ -3114,10 +3023,10 @@
         <v>701</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>142</v>
+        <v>127</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
       <c r="D16" s="2">
         <v>0</v>
@@ -3134,10 +3043,10 @@
         <v>702</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="D17" s="2">
         <v>50</v>
@@ -3154,10 +3063,10 @@
         <v>801</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>146</v>
+        <v>131</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="D18" s="2">
         <v>0</v>
@@ -3174,10 +3083,10 @@
         <v>802</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="D19" s="2">
         <v>0</v>
@@ -3194,10 +3103,10 @@
         <v>901</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="D20" s="2">
         <v>0</v>
@@ -3214,10 +3123,10 @@
         <v>902</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>152</v>
+        <v>137</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>153</v>
+        <v>138</v>
       </c>
       <c r="D21" s="2">
         <v>300</v>
@@ -3234,10 +3143,10 @@
         <v>1001</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>155</v>
+        <v>140</v>
       </c>
       <c r="D22" s="2">
         <v>0</v>
@@ -3254,10 +3163,10 @@
         <v>1002</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>156</v>
+        <v>141</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>157</v>
+        <v>142</v>
       </c>
       <c r="D23" s="2">
         <v>0</v>
@@ -3274,10 +3183,10 @@
         <v>1101</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>158</v>
+        <v>143</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="D24" s="2">
         <v>0</v>
@@ -3294,10 +3203,10 @@
         <v>1102</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>160</v>
+        <v>145</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="D25" s="2">
         <v>150</v>
@@ -3314,10 +3223,10 @@
         <v>1201</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>162</v>
+        <v>147</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="D26" s="2">
         <v>0</v>
@@ -3334,10 +3243,10 @@
         <v>1202</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>164</v>
+        <v>149</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>165</v>
+        <v>150</v>
       </c>
       <c r="D27" s="2">
         <v>0</v>
@@ -3354,10 +3263,10 @@
         <v>1301</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>166</v>
+        <v>151</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
       <c r="D28" s="2">
         <v>0</v>
@@ -3374,10 +3283,10 @@
         <v>1302</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>168</v>
+        <v>153</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="D29" s="2">
         <v>0</v>
@@ -3419,28 +3328,28 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="D1" t="s">
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="F1" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="G1" t="s">
-        <v>172</v>
+        <v>157</v>
       </c>
       <c r="H1" t="s">
-        <v>173</v>
+        <v>158</v>
       </c>
       <c r="I1" t="s">
-        <v>174</v>
+        <v>159</v>
       </c>
       <c r="J1" t="s">
-        <v>175</v>
+        <v>160</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -3480,13 +3389,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="C3" t="s">
-        <v>177</v>
+        <v>162</v>
       </c>
       <c r="D3" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -3500,13 +3409,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="C4" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="D4" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -3520,13 +3429,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="C5" t="s">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="D5" t="s">
-        <v>184</v>
+        <v>169</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -3540,13 +3449,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="C6" t="s">
-        <v>186</v>
+        <v>171</v>
       </c>
       <c r="D6" t="s">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -3560,13 +3469,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="C7" t="s">
-        <v>189</v>
+        <v>174</v>
       </c>
       <c r="D7" t="s">
-        <v>190</v>
+        <v>175</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -3580,13 +3489,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="C8" t="s">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="D8" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -3600,13 +3509,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="C9" t="s">
-        <v>195</v>
+        <v>180</v>
       </c>
       <c r="D9" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -3620,13 +3529,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>197</v>
+        <v>182</v>
       </c>
       <c r="C10" t="s">
-        <v>198</v>
+        <v>183</v>
       </c>
       <c r="D10" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -3640,13 +3549,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="C11" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="D11" t="s">
-        <v>202</v>
+        <v>187</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -3660,13 +3569,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>203</v>
+        <v>188</v>
       </c>
       <c r="C12" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="D12" t="s">
-        <v>205</v>
+        <v>190</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -3680,13 +3589,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>206</v>
+        <v>191</v>
       </c>
       <c r="C13" t="s">
-        <v>207</v>
+        <v>192</v>
       </c>
       <c r="D13" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="E13">
         <v>1</v>
@@ -3700,13 +3609,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="C14" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="D14" t="s">
-        <v>211</v>
+        <v>196</v>
       </c>
       <c r="E14">
         <v>3</v>
@@ -3720,13 +3629,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>212</v>
+        <v>197</v>
       </c>
       <c r="C15" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="D15" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="E15">
         <v>2</v>
@@ -3740,13 +3649,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="C16" t="s">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="D16" t="s">
-        <v>217</v>
+        <v>202</v>
       </c>
       <c r="E16">
         <v>3</v>
@@ -3760,13 +3669,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>218</v>
+        <v>203</v>
       </c>
       <c r="C17" t="s">
-        <v>219</v>
+        <v>204</v>
       </c>
       <c r="D17" t="s">
-        <v>220</v>
+        <v>205</v>
       </c>
       <c r="E17">
         <v>2</v>
@@ -3780,13 +3689,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>221</v>
+        <v>206</v>
       </c>
       <c r="C18" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="D18" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="E18">
         <v>2</v>
@@ -3800,13 +3709,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>224</v>
+        <v>209</v>
       </c>
       <c r="C19" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="D19" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="E19">
         <v>2</v>
@@ -3820,13 +3729,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>227</v>
+        <v>212</v>
       </c>
       <c r="C20" t="s">
-        <v>228</v>
+        <v>213</v>
       </c>
       <c r="D20" t="s">
-        <v>229</v>
+        <v>214</v>
       </c>
       <c r="E20">
         <v>3</v>
@@ -3840,13 +3749,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="C21" t="s">
-        <v>231</v>
+        <v>216</v>
       </c>
       <c r="D21" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
       <c r="E21">
         <v>3</v>
@@ -3860,13 +3769,13 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>233</v>
+        <v>218</v>
       </c>
       <c r="C22" t="s">
-        <v>234</v>
+        <v>219</v>
       </c>
       <c r="D22" t="s">
-        <v>235</v>
+        <v>220</v>
       </c>
       <c r="E22">
         <v>3</v>
@@ -3880,13 +3789,13 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>236</v>
+        <v>221</v>
       </c>
       <c r="C23" t="s">
-        <v>237</v>
+        <v>222</v>
       </c>
       <c r="D23" t="s">
-        <v>238</v>
+        <v>223</v>
       </c>
       <c r="E23">
         <v>3</v>
@@ -3918,10 +3827,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>239</v>
+        <v>224</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>240</v>
+        <v>225</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:4">
@@ -3935,7 +3844,7 @@
         <v>6</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>241</v>
+        <v>226</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" spans="1:4">
@@ -3949,7 +3858,7 @@
         <v>8</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>242</v>
+        <v>227</v>
       </c>
     </row>
   </sheetData>
